--- a/assets/docs/lop1/Tieng Anh - Lop 1.xlsx
+++ b/assets/docs/lop1/Tieng Anh - Lop 1.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Unit 1: In the school playground – Lesson 1 (1, 2) &amp; Lesson 2 (3, 4, 5)</t>
+          <t>Unit 1: In the school playground – Lesson 1 (Activities 1–2)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 1.3.CB1a: Guide pupils to access and open the lesson audio files on a safe digital learning resources website.
+          <t>Digital competence 1.1.CB1a: Listen to the word audio on the class computer and point to the right pictures on the projector (Bill, ball, bike and book).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -585,7 +585,7 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Unit 1: In the school playground – Lesson 3</t>
+          <t>Unit 1: In the school playground – Lesson 2 (Activities 3–5)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -600,30 +600,31 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.3.CB1a: Guide pupils to access and open the lesson audio files on a safe digital learning resources website.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Me and my family</t>
+          <t>Me and my friends</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Unit 2: In the dining room</t>
+          <t>Unit 1: In the school playground</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Unit 2: In the dining room – Lesson 1 &amp; 2</t>
+          <t>Unit 1: In the school playground – Lesson 3 (Activities 6–8)</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -638,14 +639,15 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.1.CB1a: Listen to the lesson audio on the class computer and point to the right character on the screen to find the information they hear.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -661,7 +663,7 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unit 2: In the dining room – Lesson 3</t>
+          <t>Unit 2: In the dining room – Lesson 1 (Activities 1–2)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -676,7 +678,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 3.1.CB1a: Practise drawing a simple birthday cake in Paint
+          <t>Digital competence 1.1.CB1a: Look at the pictures on the projector and listen to the audio on the class computer to find the right word (cake, car, cat, cup).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -684,7 +686,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -692,11 +694,15 @@
           <t>Me and my family</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2: In the dining room</t>
+        </is>
+      </c>
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Fun time 1</t>
+          <t>Unit 2: In the dining room – Lesson 2 (Activities 3–5)</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -711,30 +717,31 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 2 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Me and the world around</t>
+          <t>Me and my family</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Unit 3: At the street market</t>
+          <t>Unit 2: In the dining room</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Unit 3: At the street market – Lesson 1 &amp; 2</t>
+          <t>Unit 2: In the dining room – Lesson 3 (Activities 6–8)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -749,7 +756,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 1.1.CB1b: Search safely for pictures of a country market
+          <t>Digital competence 3.1.CB1a: Practise drawing a simple birthday cake in Paint
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -757,23 +764,19 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Me and my friends</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Unit 3: At the street market</t>
-        </is>
-      </c>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Unit 3: At the street market – Lesson 3</t>
+          <t>Fun time 1 – Lesson 1</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -788,7 +791,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>AI 1.C1.3: How an AI camera scans images and recognises circles and squares in real life.
+          <t>Digital competence 1.1.CB1a: Look at the word pictures of Units 1 and 2 on the projector and find the right picture when they hear a word.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -796,23 +799,19 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Me and my family</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Unit 4: In the bedroom</t>
-        </is>
-      </c>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Unit 4: In the bedroom – Lesson 1 &amp; 2</t>
+          <t>Fun time 1 – Lesson 2</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -827,30 +826,31 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.2.CB1a: Look at the word pictures of Units 1 and 2 in a picture quiz on the projector and choose the right answer with the class.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Me and my family</t>
+          <t>Me and the world around</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Unit 4: In the bedroom</t>
+          <t>Unit 3: At the street market</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Unit 4: In the bedroom – Lesson 3</t>
+          <t>Unit 3: At the street market – Lesson 1 (Activities 1–2)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -865,26 +865,31 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.1.CB1b: Search safely for pictures of a country market
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Unit 5: At the fish and chip shop</t>
+          <t>Unit 3: At the street market</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Unit 5: At the fish and chip shop – Lesson 1 &amp; 2</t>
+          <t>Unit 3: At the street market – Lesson 2 (Activities 3–5)</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -898,6 +903,303 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 3 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.C1.3: How an AI camera scans images and recognises circles and squares in real life.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the audio on the class computer and point to the right pictures in the Pupil’s Book (desk, dog, door, duck).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 4 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Watch and listen to the song on hoclieu.vn on the projector and follow the words and the actions.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Review 1 – Phil and Sue</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the Phil and Sue story pictures on the projector and find simple information (who, what they see) to answer the teacher’s questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Review 1 – Self-check – Part 1</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the Self-check audio on the class computer and check their answers on the screen with the teacher’s guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Review 1 – Self-check – Part 2</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 5.2.CB1a: Choose a simple revision tool the teacher prepares (the audio, digital flashcards or a picture game) to practise the words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>AI 1.C1.1: Recognise the AI system in automatic ordering machines that quickly identifies fish dishes.
 Ethics: Know how to say "Thank you" when receiving food from parents or staff.
@@ -905,78 +1207,117 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 5 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.D1.1: For a robot to know the types of milk, pupils need to show the machine pictures of strawberry milk and plain milk cartons so that it does not learn wrongly.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Me and my school</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5: At the fish and chip shop</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5: At the fish and chip shop – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>AI 1.D1.1: For a robot to know the types of milk, pupils need to show the machine pictures of strawberry milk and plain milk cartons so that it does not learn wrongly.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Me and my school</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Unit 6: In the classroom</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Unit 6: In the classroom – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>AI 1.C1.1: Recognise AI in the smart interactive board that helps the teacher practise writing the letter Pp, pen, pencil.
 Digital competence 4.1.CB1a: Turn off the computer at the end of the lesson to protect the device.
@@ -984,39 +1325,78 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Me and my school</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Unit 6: In the classroom</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Unit 6: In the classroom – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 6 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>AI 1.A1.1: Discussion: Humans decide to use pencils to draw creative pictures; AI only follows commands.
 Digital competence 3.1.CB1a: Practise drawing a classroom object (a rectangle) on the computer.
@@ -1024,69 +1404,109 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Fun time 2</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>AI 1.C1.1: Compare how fast pupils find words with how fast AI scans data to find the answer in an instant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 2 – Lesson 1</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.C1.1: Compare how fast pupils find words with how fast AI scans data to find the answer in an instant.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 2 – Lesson 2</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the word pictures of Units 5 and 6 in a picture quiz on the projector and choose the right answer with the class.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Me and my family</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Unit 7: In the garden</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7: In the garden – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7: In the garden – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>AI 1.C1.1: Recognise smart (AI) devices that automatically water the garden when the soil is dry.
 Ethics: Love nature and protect green trees.
@@ -1094,416 +1514,26 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Me and my family</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7: In the garden</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7: In the garden – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Me and my family</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Unit 8: In the park</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Unit 8: In the park – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Semester I Test &amp; Feedback – Self-check</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Me and the world around</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Unit 9: In the shop</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Unit 9: In the shop – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Me and the world around</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Unit 9: In the shop</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Unit 9: In the shop – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Me and the world around</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10: At the zoo</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10: At the zoo – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence 1.1.CB1b: Search the Internet for videos of monkey sounds under the teacher's safe guidance.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Me and the world around</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10: At the zoo</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10: At the zoo – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>AI 1.A1.1: Discussion: Humans decide what to feed animals; AI can only suggest menus based on available data.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Fun time 3</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Me and my friends</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11: At the bus stop</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11: At the bus stop – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence 4.3.CB1a: Health risk warning: Do not walk while looking at a phone, so as to stay safe in the sun.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Me and my friends</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11: At the bus stop</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11: At the bus stop – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Unit 12: At the lake</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Unit 12: At the lake – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence 3.1.CB1a: Practise drawing a simple digital leaf or lemon (lemons) on the computer.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Unit 12: At the lake</t>
+          <t>Unit 7: In the garden</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Unit 12: At the lake – Lesson 3</t>
+          <t>Unit 7: In the garden – Lesson 2 (Activities 3–5)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1518,30 +1548,31 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 7 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Me and my school</t>
+          <t>Me and my family</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Unit 13: In the school canteen</t>
+          <t>Unit 7: In the garden</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Unit 13: In the school canteen – Lesson 1, 2</t>
+          <t>Unit 7: In the garden – Lesson 3 (Activities 6–8)</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1556,30 +1587,31 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.1.CB1a: Look at the poster on the projector and listen to the song audio to find the girl, the goat and the gate.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Me and my school</t>
+          <t>Me and my family</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Unit 13: In the school canteen</t>
+          <t>Unit 8: In the park</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Unit 13: In the school canteen – Lesson 3</t>
+          <t>Unit 8: In the park – Lesson 1 (Activities 1–2)</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1594,30 +1626,31 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.1.CB1a: Listen to the audio on the class computer and point to the right body part or picture (hair, hand, head, horse).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Me and my school</t>
+          <t>Me and my family</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Unit 14: In the toy shop</t>
+          <t>Unit 8: In the park</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Unit 14: In the toy shop – Lesson 1, 2</t>
+          <t>Unit 8: In the park – Lesson 2 (Activities 3–5)</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1632,7 +1665,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 4.2.CB1b: Information security: Do not share photos of expensive gifts online, so that bad people cannot take advantage of them.
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 8 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1640,15 +1673,23 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr"/>
-      <c r="C34" s="4" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Unit 8: In the park</t>
+        </is>
+      </c>
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Fun time 4</t>
+          <t>Unit 8: In the park – Lesson 3 (Activities 6–8)</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1663,26 +1704,27 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 3.3.CB1a: Respect copyright: Write your name on your drawing before submitting it to the teacher on the interactive board.</t>
+          <t>Digital competence 1.1.CB1a: Listen to the song audio on the class computer and touch the right body part (hair, hand, head).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Unit 15: At the football match</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Unit 15: At the football match – Lesson 1, 2</t>
+          <t>Review 2 – Phil and Sue</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1697,30 +1739,26 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.2.CB1a: Look at the Phil and Sue story pictures on the projector and find simple information (who, what they see) to answer the teacher’s questions.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Me and my school</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Unit 15: At the football match</t>
-        </is>
-      </c>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
       <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Unit 15: At the football match – Lesson 3</t>
+          <t>Review 2 – Self-check – Part 1</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1735,26 +1773,26 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.1.CB1a: Listen to the Self-check audio on the class computer and check their answers on the screen with the teacher’s guidance.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr"/>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Unit 16: At home</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Unit 16: At home – Lesson 1, 2</t>
+          <t>Review 2 – Self-check – Part 2</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1769,23 +1807,26 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 1.3.CB1b: Pupils sort pictures of houses into the "My Home" folder on the class computer.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 5.2.CB1a: Choose a simple revision tool the teacher prepares (the audio, digital flashcards or a picture game) to practise the words.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Reserve / Consolidation</t>
+        </is>
+      </c>
       <c r="C38" s="4" t="inlineStr"/>
       <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Review 4: Self-check</t>
+          <t>Reserve period 1</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1798,7 +1839,1325 @@
           <t>35</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 2.4.CB1a: Take part in a simple picture quiz on the projector, taking turns and cheering politely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the flashcard pictures on the projector and listen to the audio to find the right things in the shop (clocks, locks, mops, pots).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 9 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Count the things in the pictures on the projector and listen to the audio to check their answers.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1b: Search the Internet for videos of monkey sounds under the teacher's safe guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 10 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.A1.1: Discussion: Humans decide what to feed animals; AI can only suggest menus based on available data.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 3 – Lesson 1</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the pictures of Units 9 and 10 on the projector and find the right picture when they hear a word.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 3 – Lesson 2</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the word pictures of Units 9 and 10 in a picture quiz on the projector and choose the right answer with the class.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 4.3.CB1a: Know the health risk of walking while looking at a phone, and stay safe in the sun.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 11 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the pictures on the projector and listen to the audio to find who is running (he or she).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 3.1.CB1a: Practise drawing a simple digital leaf or lemon (lemons) on the computer.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 12 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the pictures on the projector and listen to the song audio to find Lucy, the lake, the leaf and the lemons.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Review 3 – Phil and Sue</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the Phil and Sue story pictures on the projector and find simple information (who, what they see) to answer the teacher’s questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Review 3 – Self-check – Part 1</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the Self-check audio on the class computer and check their answers on the screen with the teacher’s guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Review 3 – Self-check – Part 2</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 5.2.CB1a: Choose a simple revision tool the teacher prepares (the audio, digital flashcards or a picture game) to practise the words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the audio on the class computer and point to the right food pictures (bananas, noodles, nuts).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 13 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the canteen pictures on the projector and listen to the audio to find what he or she is having.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 4.2.CB1b: Information security: Do not share photos of expensive gifts online, so that bad people cannot take advantage of them.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 14 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the toy shop picture on the projector and listen to the audio to find the toys they hear.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 4 – Lesson 1</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 3.3.CB1a: Respect copyright: Write your name on your drawing before submitting it to the teacher on the interactive board.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 4 – Lesson 2</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the word pictures of Units 13 and 14 in a picture quiz on the projector and choose the right answer with the class.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the audio on the class computer and point to the right pictures (face, father, foot, football).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 15 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Watch the song pictures on the projector, listen and point to the right body parts.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1b: Pupils sort pictures of houses into the "My Home" folder on the class computer.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 16 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Count the things in the picture on the projector and listen to the audio to check the numbers (six to ten).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Review 4 – Phil and Sue</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the Phil and Sue story pictures on the projector and find simple information (who, what they see) to answer the teacher’s questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Review 4 – Self-check – Part 1</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the Self-check audio on the class computer and check their answers on the screen with the teacher’s guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Review 4 – Self-check – Part 2</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 5.2.CB1a: Choose a simple revision tool the teacher prepares (the audio, digital flashcards or a picture game) to practise the words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Reserve / Consolidation</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Reserve period 2</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 2.4.CB1a: Take part in a simple picture quiz on the projector, taking turns and cheering politely.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
